--- a/出力/全物件一覧.xlsx
+++ b/出力/全物件一覧.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="未確認・食い違い" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'住戸一覧'!$A$4:$M$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'住戸一覧'!$A$4:$N$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'未確認・食い違い'!$A$3:$I$360</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -486,6 +486,7 @@
     <col width="34" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,7 +499,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>写真枚数＝住戸の写真＋間取図の保存枚数（実ファイル数）。共用部の写真は含まない。詳細・出典は各マンションフォルダの物件情報.mdを参照。</t>
+          <t>写真枚数＝元付HP・販売図面由来の住戸写真＋間取図（実ファイル数）。他社掲載写真（要許可確認）は別列。共用部の写真は含まない。詳細・出典は各マンションフォルダの物件情報.mdを参照。</t>
         </is>
       </c>
     </row>
@@ -568,6 +569,11 @@
           <t>未確認項目数</t>
         </is>
       </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>他社掲載写真（要許可確認）</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -631,6 +637,9 @@
       <c r="M5" s="4" t="n">
         <v>18</v>
       </c>
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -694,6 +703,9 @@
       <c r="M6" s="4" t="n">
         <v>19</v>
       </c>
+      <c r="N6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -757,6 +769,9 @@
       <c r="M7" s="4" t="n">
         <v>19</v>
       </c>
+      <c r="N7" s="4" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -820,6 +835,9 @@
       <c r="M8" s="4" t="n">
         <v>18</v>
       </c>
+      <c r="N8" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -883,6 +901,9 @@
       <c r="M9" s="4" t="n">
         <v>15</v>
       </c>
+      <c r="N9" s="4" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -946,6 +967,9 @@
       <c r="M10" s="4" t="n">
         <v>16</v>
       </c>
+      <c r="N10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1004,11 +1028,14 @@
         </is>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" s="4" t="n">
         <v>14</v>
       </c>
+      <c r="N11" s="4" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1072,6 +1099,9 @@
       <c r="M12" s="4" t="n">
         <v>11</v>
       </c>
+      <c r="N12" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1135,6 +1165,9 @@
       <c r="M13" s="4" t="n">
         <v>8</v>
       </c>
+      <c r="N13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1198,6 +1231,9 @@
       <c r="M14" s="4" t="n">
         <v>18</v>
       </c>
+      <c r="N14" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1261,6 +1297,9 @@
       <c r="M15" s="4" t="n">
         <v>11</v>
       </c>
+      <c r="N15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1324,6 +1363,9 @@
       <c r="M16" s="4" t="n">
         <v>14</v>
       </c>
+      <c r="N16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1387,6 +1429,9 @@
       <c r="M17" s="4" t="n">
         <v>15</v>
       </c>
+      <c r="N17" s="4" t="n">
+        <v>29</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1450,6 +1495,9 @@
       <c r="M18" s="4" t="n">
         <v>11</v>
       </c>
+      <c r="N18" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1513,6 +1561,9 @@
       <c r="M19" s="4" t="n">
         <v>17</v>
       </c>
+      <c r="N19" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1571,11 +1622,14 @@
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M20" s="4" t="n">
         <v>12</v>
       </c>
+      <c r="N20" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1638,6 +1692,9 @@
       </c>
       <c r="M21" s="4" t="n">
         <v>15</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>62</v>
       </c>
     </row>
     <row r="22">
@@ -1654,9 +1711,13 @@
         <f>SUM(M5:M21)</f>
         <v/>
       </c>
+      <c r="N22" s="5">
+        <f>SUM(N5:N21)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:M21"/>
+  <autoFilter ref="A4:N21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
